--- a/Data/GP2_FINAL_WEIGHT.xlsx
+++ b/Data/GP2_FINAL_WEIGHT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106B87F7-F722-4D3C-92C9-0BACD4D3725E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7C4D62-3A89-4A9D-B883-EF3089E09E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{46041644-3AF4-4E5F-99C5-C935C4B9809B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{46041644-3AF4-4E5F-99C5-C935C4B9809B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Data/GP2_FINAL_WEIGHT.xlsx
+++ b/Data/GP2_FINAL_WEIGHT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7C4D62-3A89-4A9D-B883-EF3089E09E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCC95B7-3A34-474C-9FB5-902A63CCCD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{46041644-3AF4-4E5F-99C5-C935C4B9809B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="10">
   <si>
     <t>diet</t>
   </si>
@@ -55,15 +55,33 @@
   <si>
     <t>males</t>
   </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -429,14 +447,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6661BA-7EB0-4FF8-98EF-238B29CD3800}">
   <dimension ref="A1:D71"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="1"/>
-    <col min="3" max="3" width="8.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.7109375" style="1"/>
+    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,9 +468,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -464,9 +482,9 @@
         <v>690</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>1</v>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -478,9 +496,9 @@
         <v>591</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>1</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -492,9 +510,9 @@
         <v>593</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>1</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -506,9 +524,9 @@
         <v>418</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>1</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
@@ -520,9 +538,9 @@
         <v>526</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>1</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
@@ -534,9 +552,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
-        <v>1</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
@@ -548,9 +566,9 @@
         <v>570</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
-        <v>1</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
@@ -562,9 +580,9 @@
         <v>754</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
-        <v>1</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
@@ -576,9 +594,9 @@
         <v>770</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
-        <v>1</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
@@ -590,9 +608,9 @@
         <v>591</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
-        <v>1</v>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
@@ -604,9 +622,9 @@
         <v>690</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
-        <v>1</v>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
@@ -618,9 +636,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
-        <v>1</v>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
@@ -632,9 +650,9 @@
         <v>564</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
-        <v>1</v>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B15" s="1">
         <v>14</v>
@@ -646,9 +664,9 @@
         <v>709</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
-        <v>1</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B16" s="1">
         <v>15</v>
@@ -660,9 +678,9 @@
         <v>801</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
-        <v>1</v>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -674,9 +692,9 @@
         <v>642</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
-        <v>1</v>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B18" s="1">
         <v>17</v>
@@ -688,9 +706,9 @@
         <v>708</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
-        <v>1</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B19" s="1">
         <v>18</v>
@@ -702,9 +720,9 @@
         <v>783</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
-        <v>2</v>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B20" s="1">
         <v>1</v>
@@ -716,9 +734,9 @@
         <v>571</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
-        <v>2</v>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -730,9 +748,9 @@
         <v>605</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
-        <v>2</v>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B22" s="1">
         <v>3</v>
@@ -744,9 +762,9 @@
         <v>631</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
-        <v>2</v>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B23" s="1">
         <v>4</v>
@@ -758,9 +776,9 @@
         <v>690</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
-        <v>2</v>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B24" s="1">
         <v>5</v>
@@ -772,9 +790,9 @@
         <v>639</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
-        <v>2</v>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B25" s="1">
         <v>6</v>
@@ -786,9 +804,9 @@
         <v>738</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
-        <v>2</v>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B26" s="1">
         <v>7</v>
@@ -800,9 +818,9 @@
         <v>710</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
-        <v>2</v>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B27" s="1">
         <v>8</v>
@@ -814,9 +832,9 @@
         <v>564</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
-        <v>2</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B28" s="1">
         <v>9</v>
@@ -828,9 +846,9 @@
         <v>617</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>2</v>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B29" s="1">
         <v>10</v>
@@ -842,9 +860,9 @@
         <v>709</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
-        <v>2</v>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B30" s="1">
         <v>11</v>
@@ -856,9 +874,9 @@
         <v>660</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
-        <v>2</v>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B31" s="1">
         <v>12</v>
@@ -870,9 +888,9 @@
         <v>801</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
-        <v>2</v>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B32" s="1">
         <v>13</v>
@@ -884,9 +902,9 @@
         <v>789</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
-        <v>2</v>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B33" s="1">
         <v>14</v>
@@ -898,9 +916,9 @@
         <v>785</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
-        <v>2</v>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B34" s="1">
         <v>15</v>
@@ -912,9 +930,9 @@
         <v>674</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
-        <v>2</v>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B35" s="1">
         <v>16</v>
@@ -926,9 +944,9 @@
         <v>750</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
-        <v>2</v>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B36" s="1">
         <v>17</v>
@@ -940,9 +958,9 @@
         <v>868</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
-        <v>3</v>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B37" s="1">
         <v>1</v>
@@ -954,9 +972,9 @@
         <v>700</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
-        <v>3</v>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B38" s="1">
         <v>2</v>
@@ -968,9 +986,9 @@
         <v>656</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
-        <v>3</v>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B39" s="1">
         <v>3</v>
@@ -982,9 +1000,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
-        <v>3</v>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B40" s="1">
         <v>4</v>
@@ -996,9 +1014,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
-        <v>3</v>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B41" s="1">
         <v>5</v>
@@ -1010,9 +1028,9 @@
         <v>677</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
-        <v>3</v>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B42" s="1">
         <v>6</v>
@@ -1024,9 +1042,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
-        <v>3</v>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B43" s="1">
         <v>7</v>
@@ -1038,9 +1056,9 @@
         <v>581</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
-        <v>3</v>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B44" s="1">
         <v>8</v>
@@ -1052,9 +1070,9 @@
         <v>572</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
-        <v>3</v>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B45" s="1">
         <v>9</v>
@@ -1066,9 +1084,9 @@
         <v>800</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
-        <v>3</v>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B46" s="1">
         <v>10</v>
@@ -1080,9 +1098,9 @@
         <v>613</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
-        <v>3</v>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B47" s="1">
         <v>11</v>
@@ -1094,9 +1112,9 @@
         <v>787</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
-        <v>3</v>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B48" s="1">
         <v>12</v>
@@ -1108,9 +1126,9 @@
         <v>570</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>3</v>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B49" s="1">
         <v>13</v>
@@ -1122,9 +1140,9 @@
         <v>896</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
-        <v>3</v>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B50" s="1">
         <v>14</v>
@@ -1136,9 +1154,9 @@
         <v>843</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>3</v>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B51" s="1">
         <v>15</v>
@@ -1150,9 +1168,9 @@
         <v>685</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
-        <v>3</v>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B52" s="1">
         <v>16</v>
@@ -1164,9 +1182,9 @@
         <v>823</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>3</v>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B53" s="1">
         <v>17</v>
@@ -1178,9 +1196,9 @@
         <v>539</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
-        <v>4</v>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B54" s="1">
         <v>1</v>
@@ -1192,9 +1210,9 @@
         <v>699</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
-        <v>4</v>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B55" s="1">
         <v>2</v>
@@ -1206,9 +1224,9 @@
         <v>879</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>4</v>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B56" s="1">
         <v>3</v>
@@ -1220,9 +1238,9 @@
         <v>836</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
-        <v>4</v>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B57" s="1">
         <v>4</v>
@@ -1234,9 +1252,9 @@
         <v>679</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
-        <v>4</v>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B58" s="1">
         <v>5</v>
@@ -1248,9 +1266,9 @@
         <v>779</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
-        <v>4</v>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B59" s="1">
         <v>6</v>
@@ -1262,9 +1280,9 @@
         <v>689</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
-        <v>4</v>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B60" s="1">
         <v>7</v>
@@ -1276,9 +1294,9 @@
         <v>798</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
-        <v>4</v>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B61" s="1">
         <v>8</v>
@@ -1290,9 +1308,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="1">
-        <v>4</v>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B62" s="1">
         <v>9</v>
@@ -1304,9 +1322,9 @@
         <v>722</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
-        <v>4</v>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B63" s="1">
         <v>10</v>
@@ -1318,9 +1336,9 @@
         <v>604</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
-        <v>4</v>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B64" s="1">
         <v>11</v>
@@ -1332,9 +1350,9 @@
         <v>580</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
-        <v>4</v>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B65" s="1">
         <v>12</v>
@@ -1346,9 +1364,9 @@
         <v>687</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
-        <v>4</v>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B66" s="1">
         <v>13</v>
@@ -1360,9 +1378,9 @@
         <v>700</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
-        <v>4</v>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B67" s="1">
         <v>14</v>
@@ -1374,9 +1392,9 @@
         <v>716</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
-        <v>4</v>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B68" s="1">
         <v>15</v>
@@ -1388,9 +1406,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="1">
-        <v>4</v>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B69" s="1">
         <v>16</v>
@@ -1402,9 +1420,9 @@
         <v>464</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="1">
-        <v>4</v>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B70" s="1">
         <v>17</v>
@@ -1416,9 +1434,9 @@
         <v>649</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="1">
-        <v>4</v>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B71" s="1">
         <v>18</v>
@@ -1431,6 +1449,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>